--- a/registration_forms/040_financial_governance_session_registration_form--registration_forms.xlsx
+++ b/registration_forms/040_financial_governance_session_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial_governance_session'}</t>
+          <t>financial_governance_session</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Financial Governance Session'}</t>
+          <t>Financial Governance Session</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'financial_planning'}</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Financial Planning'}</t>
+          <t>Financial Planning</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'risk_management'}</t>
+          <t>risk_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Risk Management'}</t>
+          <t>Risk Management</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'financial_analysis'}</t>
+          <t>financial_analysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Financial Analysis'}</t>
+          <t>Financial Analysis</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'financial_modeling'}</t>
+          <t>financial_modeling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Financial Modeling'}</t>
+          <t>Financial Modeling</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'financial_reporting'}</t>
+          <t>financial_reporting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Financial Reporting'}</t>
+          <t>Financial Reporting</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'undisclosed'}</t>
+          <t>undisclosed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Undisclosed'}</t>
+          <t>Undisclosed</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
